--- a/real_estate_forms/020_mortgage_lien_release_form--real_estate_forms.xlsx
+++ b/real_estate_forms/020_mortgage_lien_release_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,38 +520,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>mortgage_lien_release_form_form</t>
+          <t>loan_amount</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mortgage Lien Release Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Loan Amount</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the total amount of the loan</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>loan_amount</t>
+          <t>lender_info</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Loan Amount</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Lender Information</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Provide information about the lender</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,35 +574,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lender_name</t>
+          <t>property_address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lender</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Property Address</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter the property address</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lender_phone</t>
+          <t>loan_release_dates</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lender Phone</t>
+          <t>Loan and Release Dates</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +619,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lender_email</t>
+          <t>lien_and_release_amounts</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lender Email</t>
+          <t>Lien and Release Amounts</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,66 +642,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>property_address</t>
+          <t>payment_confirmation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Property Address</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Payment Confirmation</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Confirm that payment has been made</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>loan_date</t>
+          <t>release_instructions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Loan Date</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Release Instructions</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Provide instructions for release</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>release_date</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Release Date</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Additional Comments</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter any additional comments</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +728,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lien_amount</t>
+          <t>release_fees</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lien Amount</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Release Fees</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter any release fees</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +750,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>payment_confirmation</t>
+          <t>lender_fees</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Payment Confirmation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Lender Fees</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter any lender fees</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,338 +782,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>lender_fees</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>release_fees</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Release Fees</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>release_instructions</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Release Instructions</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>lender_comments</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Lender Comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>release_date_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Release Date</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>lender_fees_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>release_fees_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Release Fees</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>release_instructions_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Release Instructions</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>lender_comments_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lender Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>release_date_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Release Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>lender_fees_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Lender Fees</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>release_fees_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Release Fees</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>release_instructions_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Release Instructions</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>lender_comments_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Lender Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +808,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,32 +836,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>payment_confirmation_choices</t>
+          <t>lender_info_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>lender_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Lender Name</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>lender_info_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>lender_phone</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lender Phone</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>lender_info_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>lender_email</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lender Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>loan_release_dates_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>loan_date</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Loan Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>loan_release_dates_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>release_date</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Release Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>lien_and_release_amounts_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lien_amount</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lien Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lien_and_release_amounts_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>release_amount</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Release Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>payment_confirmation_choices</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>payment_confirmation_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
